--- a/data_generator/T2/Opinie.xlsx
+++ b/data_generator/T2/Opinie.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Opinie" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Opinie" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MCROSO7968</t>
+          <t>MCIDML3774</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -471,12 +471,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-04-02</t>
+          <t>2022-02-26</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -491,20 +491,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MCDOKO9776</t>
+          <t>MCSYHO2501</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -512,27 +512,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Świetny instruktor, zajęcia bardzo motywujące!</t>
+          <t>Zajęcia idealne na początek dnia, dużo energii i pozytywnej muzyki.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MCELKR6970</t>
+          <t>MCKOZB2668</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2022-12-29</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -547,15 +547,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MCGALE8579</t>
+          <t>MCPAMA6292</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-04-07</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -568,55 +568,55 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sala za mała, było zbyt tłoczno i duszno.</t>
+          <t>Instruktor mówił zbyt cicho, trudno było zrozumieć polecenia.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MCADTW6897</t>
+          <t>MCMIKU1231</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2022-03-21</t>
+          <t>2022-08-11</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zajęcia idealne na początek dnia, dużo energii i pozytywnej muzyki.</t>
+          <t>Instruktor mówił zbyt cicho, trudno było zrozumieć polecenia.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MCADTW6897</t>
+          <t>MCRAJA9393</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2022-11-23</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -624,42 +624,42 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Świetny instruktor, zajęcia bardzo motywujące!</t>
+          <t>Sala czysta, sprzęt w doskonałym stanie – polecam!</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MCURDU8051</t>
+          <t>MCPAMA6292</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Instruktor tłumaczy wszystko bardzo jasno i z uśmiechem.</t>
+          <t>Zajęcia rozpoczęły się z dużym opóźnieniem.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MCKASA9992</t>
+          <t>MCKAAC3140</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -667,259 +667,259 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sprzęt w złym stanie, kilka mat było podartych.</t>
+          <t>Super atmosfera i dobrze dobrane tempo ćwiczeń.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MCRAZA3008</t>
+          <t>MCDAEN7847</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2022-08-11</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Instruktor tłumaczy wszystko bardzo jasno i z uśmiechem.</t>
+          <t>Super atmosfera i dobrze dobrane tempo ćwiczeń.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MCOSME2749</t>
+          <t>MCHUCI2981</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Instruktor mówił zbyt cicho, trudno było zrozumieć polecenia.</t>
+          <t>Instruktor tłumaczy wszystko bardzo jasno i z uśmiechem.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MCANAN4019</t>
+          <t>MCIDML3774</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2022-01-17</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Za dużo osób w grupie, brakowało indywidualnego podejścia.</t>
+          <t>Zajęcia rozpoczęły się z dużym opóźnieniem.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MCMEWO6948</t>
+          <t>MCSYHO2501</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Instruktor tłumaczy wszystko bardzo jasno i z uśmiechem.</t>
+          <t>Za dużo osób w grupie, brakowało indywidualnego podejścia.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MCAGKO2233</t>
+          <t>MCMAMI6342</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zajęcia idealne na początek dnia, dużo energii i pozytywnej muzyki.</t>
+          <t>Sala za mała, było zbyt tłoczno i duszno.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MCOLKR4929</t>
+          <t>MCMAKU8039</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zajęcia rozpoczęły się z dużym opóźnieniem.</t>
+          <t>Sala czysta, sprzęt w doskonałym stanie – polecam!</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MCCEME2932</t>
+          <t>MCHUCI2981</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2023-07-09</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Świetny instruktor, zajęcia bardzo motywujące!</t>
+          <t>Zajęcia idealne na początek dnia, dużo energii i pozytywnej muzyki.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MCTOSE1448</t>
+          <t>MCMAKO6326</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2022-03-21</t>
+          <t>2022-11-23</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Za dużo osób w grupie, brakowało indywidualnego podejścia.</t>
+          <t>Instruktor mówił zbyt cicho, trudno było zrozumieć polecenia.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MCKASA9992</t>
+          <t>MCJADE2444</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -939,20 +939,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MCINMA7075</t>
+          <t>MCLIGR4182</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2023-04-03</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -960,143 +960,143 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zajęcia rozpoczęły się z dużym opóźnieniem.</t>
+          <t>Instruktor mówił zbyt cicho, trudno było zrozumieć polecenia.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MCCEBA4849</t>
+          <t>MCELSW9124</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2024-04-07</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Instruktor mówił zbyt cicho, trudno było zrozumieć polecenia.</t>
+          <t>Sprzęt w złym stanie, kilka mat było podartych.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MCOLKR4929</t>
+          <t>MCLIGR4182</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
+          <t>2023-07-09</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Instruktor mówił zbyt cicho, trudno było zrozumieć polecenia.</t>
+          <t>Za dużo osób w grupie, brakowało indywidualnego podejścia.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MCMEZA8337</t>
+          <t>MCSYMI4112</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2022-11-23</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Instruktor tłumaczy wszystko bardzo jasno i z uśmiechem.</t>
+          <t>Sala za mała, było zbyt tłoczno i duszno.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MCANKI1542</t>
+          <t>MCOLNI1931</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Świetny instruktor, zajęcia bardzo motywujące!</t>
+          <t>Sprzęt w złym stanie, kilka mat było podartych.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MCOLKR4929</t>
+          <t>MCJARA7205</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1107,104 +1107,104 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MCCEBA4849</t>
+          <t>MCKAST1270</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Świetny instruktor, zajęcia bardzo motywujące!</t>
+          <t>Za dużo osób w grupie, brakowało indywidualnego podejścia.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MCNISZ2574</t>
+          <t>MCDAEN7847</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2023-03-30</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sala za mała, było zbyt tłoczno i duszno.</t>
+          <t>Instruktor tłumaczy wszystko bardzo jasno i z uśmiechem.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MCMASU6375</t>
+          <t>MCELSW9124</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2022-01-17</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Instruktor tłumaczy wszystko bardzo jasno i z uśmiechem.</t>
+          <t>Instruktor mówił zbyt cicho, trudno było zrozumieć polecenia.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MCMASU6375</t>
+          <t>MCKAST1270</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2024-04-07</t>
+          <t>2022-04-18</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1212,14 +1212,14 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sala czysta, sprzęt w doskonałym stanie – polecam!</t>
+          <t>Instruktor tłumaczy wszystko bardzo jasno i z uśmiechem.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MCEWPI7958</t>
+          <t>MCKRPO2375</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1227,40 +1227,40 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Za dużo osób w grupie, brakowało indywidualnego podejścia.</t>
+          <t>Sala za mała, było zbyt tłoczno i duszno.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MCSARA5352</t>
+          <t>MCJARA7205</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-12-29</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1268,59 +1268,59 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sala za mała, było zbyt tłoczno i duszno.</t>
+          <t>Za dużo osób w grupie, brakowało indywidualnego podejścia.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MCMEZA8337</t>
+          <t>MCMAPA9881</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2023-03-30</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sprzęt w złym stanie, kilka mat było podartych.</t>
+          <t>Świetny instruktor, zajęcia bardzo motywujące!</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MCKOWO2455</t>
+          <t>MCJARA7205</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2022-07-25</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1331,91 +1331,91 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MCRORO9263</t>
+          <t>MCKAST1270</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sala czysta, sprzęt w doskonałym stanie – polecam!</t>
+          <t>Instruktor mówił zbyt cicho, trudno było zrozumieć polecenia.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MCKLBO5136</t>
+          <t>MCBOSZ5711</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2023-03-30</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sala za mała, było zbyt tłoczno i duszno.</t>
+          <t>Zajęcia idealne na początek dnia, dużo energii i pozytywnej muzyki.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MCSARA5352</t>
+          <t>MCMAPA9881</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
+          <t>2022-02-26</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sprzęt w złym stanie, kilka mat było podartych.</t>
+          <t>Świetny instruktor, zajęcia bardzo motywujące!</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MCRORO9263</t>
+          <t>MCMIKU1231</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1436,31 +1436,31 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Instruktor mówił zbyt cicho, trudno było zrozumieć polecenia.</t>
+          <t>Sprzęt w złym stanie, kilka mat było podartych.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MCWOWI4112</t>
+          <t>MCJADE2444</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1471,76 +1471,76 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MCELWA2808</t>
+          <t>MCJUDU4380</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
+          <t>2023-03-29</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sprzęt w złym stanie, kilka mat było podartych.</t>
+          <t>Instruktor mówił zbyt cicho, trudno było zrozumieć polecenia.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MCSARA5352</t>
+          <t>MCMAKO6326</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2022-03-21</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Super atmosfera i dobrze dobrane tempo ćwiczeń.</t>
+          <t>Za dużo osób w grupie, brakowało indywidualnego podejścia.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MCMEWO6948</t>
+          <t>MCKAKO1929</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1548,259 +1548,147 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Zajęcia rozpoczęły się z dużym opóźnieniem.</t>
+          <t>Sala za mała, było zbyt tłoczno i duszno.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MCROJA8939</t>
+          <t>MCLIGR4182</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2022-02-28</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Zajęcia idealne na początek dnia, dużo energii i pozytywnej muzyki.</t>
+          <t>Instruktor mówił zbyt cicho, trudno było zrozumieć polecenia.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MCELKR6970</t>
+          <t>MCELTR9644</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2024-09-15</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sala czysta, sprzęt w doskonałym stanie – polecam!</t>
+          <t>Sprzęt w złym stanie, kilka mat było podartych.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MCWOWI4112</t>
+          <t>MCDOCH1211</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2023-07-09</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Zajęcia idealne na początek dnia, dużo energii i pozytywnej muzyki.</t>
+          <t>Zajęcia rozpoczęły się z dużym opóźnieniem.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MCEWPI7958</t>
+          <t>MCKOBE2294</t>
         </is>
       </c>
       <c r="B44" t="n">
+        <v>18</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2024-12-29</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
         <v>2</v>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2023-01-17</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>5</v>
-      </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Instruktor tłumaczy wszystko bardzo jasno i z uśmiechem.</t>
+          <t>Instruktor mówił zbyt cicho, trudno było zrozumieć polecenia.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MCELWA2808</t>
+          <t>MCKRPO2375</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Instruktor tłumaczy wszystko bardzo jasno i z uśmiechem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>MCBOWA4133</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>3</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2023-07-17</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>06:00</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>2</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Sprzęt w złym stanie, kilka mat było podartych.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>MCERMA5501</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>8</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>3</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Za dużo osób w grupie, brakowało indywidualnego podejścia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>MCANKI1542</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>14</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Sprzęt w złym stanie, kilka mat było podartych.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>MCADTW6897</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>12</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2024-11-22</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>2</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Sala za mała, było zbyt tłoczno i duszno.</t>
+          <t>Zajęcia rozpoczęły się z dużym opóźnieniem.</t>
         </is>
       </c>
     </row>
